--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_9.xlsx
@@ -513,716 +513,716 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9920644233433547</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7395855754923701</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8638938360755033</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9933087325693604</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9733735658639748</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05306523764295792</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.741392455780688</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I2" t="n">
-        <v>0.26698530285184</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05798221021408337</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1624838785588716</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2199391753391281</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2303589321970345</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N2" t="n">
-        <v>1.005441538278842</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2401657888493903</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P2" t="n">
-        <v>123.8724664468826</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q2" t="n">
-        <v>195.7861401141064</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9917075684077333</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7395852482447689</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8571387724067822</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9929702306701652</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9720475434381752</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05545152824062369</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.741394644086905</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2802360085316902</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06091544946665382</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1705757344078098</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2235681814673101</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2354814817360883</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N3" t="n">
-        <v>1.005686238806126</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.245506415927461</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P3" t="n">
-        <v>123.784492009738</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q3" t="n">
-        <v>195.6981656769618</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9913762607662522</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7395749267451581</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8509368905883488</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9926574948218778</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9708287030285974</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05766698396473993</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.741463664002328</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2924015949225043</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06362541673142766</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1780135278457432</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2268165810391981</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2401395093789024</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N4" t="n">
-        <v>1.005913421188856</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2503627454504762</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P4" t="n">
-        <v>123.7061409417778</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q4" t="n">
-        <v>195.6198146090016</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9924477111378492</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7395732882761575</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8712439078387147</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.993674396043788</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9748145577886249</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05050219039629482</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74147462045208</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2525674316908221</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05481360625950259</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1536904383372847</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2158771336270452</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2247269240573875</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N5" t="n">
-        <v>1.005178712362618</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2342940144633745</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P5" t="n">
-        <v>123.9714771389148</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q5" t="n">
-        <v>195.8851508061386</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9910705184576</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7395583115240431</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8452681585954149</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9923699291181104</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F6" t="n">
-        <v>0.969713411922954</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05971148419051049</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.741574770062431</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3035213567634075</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06611727574902544</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1848194269624394</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2297175731073676</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2443593341587558</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N6" t="n">
-        <v>1.006123073057646</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2547622169074495</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P6" t="n">
-        <v>123.6364618241664</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q6" t="n">
-        <v>195.5501354913902</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_12</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9928568127029487</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7395432965891775</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8792090969484692</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9940676771611712</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9763739763258722</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0477665263467356</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.741675175001014</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2369429488208201</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05140568561401786</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K7" t="n">
-        <v>0.144174317217419</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2113218825873803</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2185555452207416</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N7" t="n">
-        <v>1.004898185575121</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2278599072531372</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P7" t="n">
-        <v>124.0828603408648</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q7" t="n">
-        <v>195.9965340080886</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.990789347943263</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C8" t="n">
-        <v>0.739537685092171</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8400978368926876</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9921061560769289</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F8" t="n">
-        <v>0.968695162697081</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06159167271455304</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.741712699107335</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3136634389868832</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06840296288993504</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1910331423519732</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2323156816062993</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2481766965582245</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N8" t="n">
-        <v>1.006315875696048</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2587420923272931</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P8" t="n">
-        <v>123.5744572015721</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q8" t="n">
-        <v>195.4881308687959</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9905314556437017</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7395145082182087</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8353908646281192</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9918647361016399</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9677672231754931</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06331619970920462</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.74186768297024</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3228966168190653</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07049495277110202</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1966957561201332</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2346336437131726</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2516271044804287</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N9" t="n">
-        <v>1.006492716130033</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2623393912580747</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P9" t="n">
-        <v>123.5192281259943</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q9" t="n">
-        <v>195.4329017932181</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9932902625086291</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7394893340227048</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8878022083831492</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9944883852480901</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9780538014080198</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04486804550029792</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.742036022931492</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2200867360478237</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04776010053056973</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1339234329550567</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2062260740845655</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2118207862800484</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N10" t="n">
-        <v>1.004600962851226</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2208384356814657</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P10" t="n">
-        <v>124.2080588382145</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q10" t="n">
-        <v>196.1217325054384</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9902949398172401</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7394892288164667</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8311008342166825</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9916439784555813</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9669209839609965</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0648977821298086</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.74203672644609</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3313119231917909</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07240789622655691</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2018598058407076</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2367188387767585</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2547504310689357</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N11" t="n">
-        <v>1.006654898411035</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2655956843256317</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P11" t="n">
-        <v>123.4698836590215</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q11" t="n">
-        <v>195.3835573262453</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9900791877911946</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7394637291023711</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8272104414056594</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9914426633393976</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9661527573264457</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06634051692142111</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.742207243151663</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3389433020574815</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.07415236325120177</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2065477953235031</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2385796057078831</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2575665291170829</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N12" t="n">
-        <v>1.006802842657466</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2685316694978151</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P12" t="n">
-        <v>123.4259089069829</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q12" t="n">
-        <v>195.3395825742068</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9898823773043082</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7394383370019926</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8236784675732194</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9912593477081428</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9654549404122506</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0676565895534601</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.742377040243814</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3458716076986709</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07574085834232142</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2108061198953614</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2402544623618539</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2601088032986583</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N13" t="n">
-        <v>1.006937798419903</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2711821735545332</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P13" t="n">
-        <v>123.3866210451077</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q13" t="n">
-        <v>195.3002947123315</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9897033407229964</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7394135985934882</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D14" t="n">
-        <v>0.820479972570036</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9910926656342294</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9648225388174323</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06885380799708005</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.742542466095393</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3521457626118072</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07718521774788296</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2146652571500142</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2417494666352319</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2624000914578348</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N14" t="n">
-        <v>1.007060566361374</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2735710065942663</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P14" t="n">
-        <v>123.3515394934747</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q14" t="n">
-        <v>195.2652131606986</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="15">
@@ -1232,657 +1232,657 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9937462413336331</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7394050076715818</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8970395520085195</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9949364834344612</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9798566214766558</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04181891299790646</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.742599913629738</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2019668000048528</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04387717050153823</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1229219899680132</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2004957571592885</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2044967310200984</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N15" t="n">
-        <v>1.004288291656937</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2132025802262152</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P15" t="n">
-        <v>124.3488131554354</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q15" t="n">
-        <v>196.2624868226592</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_24</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9895403338148185</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7393893910983532</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8175793865673524</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9909411152221956</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9642486766818906</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06994383594264265</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.742704341726826</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3578355404296868</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07849845592580006</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2181671660073751</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2430945942973827</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2644689697160003</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N16" t="n">
-        <v>1.007172342526982</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2757279612830502</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P16" t="n">
-        <v>123.3201254053185</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q16" t="n">
-        <v>195.2337990725424</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9942192395277003</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7392783040828448</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9068804109016324</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9954094812498336</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9817741191922779</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03865597189622262</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.743447181111039</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1826630108439337</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03977847633843421</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1112207435911839</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1940793726821933</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1966112201686939</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N17" t="n">
-        <v>1.003963950038148</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2049813668526086</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P17" t="n">
-        <v>124.5061080073849</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q17" t="n">
-        <v>196.4197816746087</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9947041526762401</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7390984950412167</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9173064437631355</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9959055756063281</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9838020644362565</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03541335543911717</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.744649565000351</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1622113467839885</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03547964243851186</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K18" t="n">
-        <v>0.09884550749823444</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1868669168858149</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1881843655544136</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N18" t="n">
-        <v>1.003631438164864</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1961957635914046</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P18" t="n">
-        <v>124.6813325154005</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q18" t="n">
-        <v>196.5950061826244</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9951911699606242</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7388482975036977</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D19" t="n">
-        <v>0.928230676184744</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E19" t="n">
-        <v>0.996420023362232</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9859231230244063</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G19" t="n">
-        <v>0.03215666861593261</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.746322637085794</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1407824164739329</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03102176981031604</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08590206098592451</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1787640934066701</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1793228056214062</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N19" t="n">
-        <v>1.003297483455572</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1869569487060911</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P19" t="n">
-        <v>124.8742708557</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q19" t="n">
-        <v>196.7879445229238</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9956679470952259</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7385085017918698</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9395401347445552</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E20" t="n">
-        <v>0.996947084492655</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9881150313795019</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02896845772149375</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.748594852575402</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I20" t="n">
-        <v>0.118597828123059</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02645459780939996</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07252626424340652</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1696528106379735</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1702012271445002</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N20" t="n">
-        <v>1.002970550563274</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1774470457491527</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P20" t="n">
-        <v>125.0830954114167</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q20" t="n">
-        <v>196.9967690786405</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9961163706588603</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7380521937349858</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9510419381149409</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9974779338002802</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9903405670832751</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02596984728666993</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.751646186652891</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09603593696662149</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02185459990679361</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K21" t="n">
-        <v>0.05894526157617087</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1594064434439882</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M21" t="n">
-        <v>0.161151628247033</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N21" t="n">
-        <v>1.002663060119639</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1680121866913681</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P21" t="n">
-        <v>125.3016382673989</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q21" t="n">
-        <v>197.2153119346227</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9965125232987895</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7374464789537025</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9624672951008885</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9980009989183829</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F22" t="n">
-        <v>0.992548278538451</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02332077275934823</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.755696604184393</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07362400272993436</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0173220547727267</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K22" t="n">
-        <v>0.04547302875133053</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1478893357050703</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1527114035013372</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N22" t="n">
-        <v>1.002391412595116</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1592126441045742</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P22" t="n">
-        <v>125.5168215617111</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q22" t="n">
-        <v>197.4304952289349</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9968248619143283</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7366494976556032</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9734452075402411</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9985011059689223</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9946677731117186</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02123216299905327</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.761026021794545</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05208977391332123</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01298844945288254</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K23" t="n">
-        <v>0.03253912640865561</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1349419537016336</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M23" t="n">
-        <v>0.145712604118701</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N23" t="n">
-        <v>1.002177237544461</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1519158913427072</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P23" t="n">
-        <v>125.7044762487503</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q23" t="n">
-        <v>197.6181499159742</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9970121263002469</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7356091401525653</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9834703962180819</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9989589254464136</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9966041297798751</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0199799251881418</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.767982897207764</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03242440418925097</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.009021280981562942</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02072279606159968</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1203845955076309</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1413503632402188</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N24" t="n">
-        <v>1.002048827679831</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1473679408389445</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P24" t="n">
-        <v>125.826054500212</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q24" t="n">
-        <v>197.7397281674358</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9970205159572981</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7342589271388023</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9918625206184204</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9993495530970378</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F25" t="n">
-        <v>0.998230290611191</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01992382351280997</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.777011777847957</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01596244677314435</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.005636353568526912</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01079938995761695</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1040640424230934</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1411517747419775</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N25" t="n">
-        <v>1.002043074772138</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1471608980171983</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P25" t="n">
-        <v>125.8316782036606</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q25" t="n">
-        <v>197.7453518708845</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_0</t>
+          <t>model_23_9_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.996782016561615</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7325178057893061</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9977452190633764</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9996427420427283</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F26" t="n">
-        <v>0.999383950580375</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02151867006993129</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.788654664329165</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004422969201916226</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.003095767161289408</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K26" t="n">
-        <v>0.003759350522613765</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08577941468153714</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1466924335810518</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N26" t="n">
-        <v>1.002206617214892</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1529374341737969</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P26" t="n">
-        <v>125.6776686906452</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q26" t="n">
-        <v>197.5913423578691</v>
+        <v>211.081772065143</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_9.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9999988643886509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.99999999999929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999998236250807</v>
       </c>
       <c r="G2" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I2" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>2.948535195063845e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001063093201132382</v>
+        <v>5.852106052195969e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>1.474270319282783e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M2" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P2" t="n">
-        <v>139.1680983979192</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q2" t="n">
-        <v>211.081772065143</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999441604761281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6592540353682896</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998765776836601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999670673945183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.999964592377926</v>
       </c>
       <c r="G3" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>3.31487535121617e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2022815240646252</v>
       </c>
       <c r="I3" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>3.2045738525452e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001063093201132382</v>
+        <v>2.714681163454087e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>2.959627507999644e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003077072415503034</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005757495420073011</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000038289959226</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.006002603919764077</v>
       </c>
       <c r="P3" t="n">
-        <v>139.1680983979192</v>
+        <v>138.6290108869649</v>
       </c>
       <c r="Q3" t="n">
-        <v>211.081772065143</v>
+        <v>210.5426845541887</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999489908568202</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6588583152549172</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998590138672087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999602882657755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999585215971278</v>
       </c>
       <c r="G4" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>3.028123087177122e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2025164406181419</v>
       </c>
       <c r="I4" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>3.66060602420128e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001063093201132382</v>
+        <v>3.273494316362075e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>3.467067680274921e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003044597495864655</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005502838437731134</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000034977698181</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00573710566247128</v>
       </c>
       <c r="P4" t="n">
-        <v>139.1680983979192</v>
+        <v>138.809964961118</v>
       </c>
       <c r="Q4" t="n">
-        <v>211.081772065143</v>
+        <v>210.7236386283419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999524525849939</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6584960027626989</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998422701720748</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999535489190405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999525982262941</v>
       </c>
       <c r="G5" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.822619948904225e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2027315249646074</v>
       </c>
       <c r="I5" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>4.095344321231829e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001063093201132382</v>
+        <v>3.829028182202911e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>3.96218625171737e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003015413960899755</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005312833470855476</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032603941718</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005539011790791222</v>
       </c>
       <c r="P5" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9505199028682</v>
       </c>
       <c r="Q5" t="n">
-        <v>211.081772065143</v>
+        <v>210.8641935700921</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999548493081938</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6581649787620412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998264400071288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999469633355379</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.999946892347059</v>
       </c>
       <c r="G6" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.680340106451064e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2029280351108901</v>
       </c>
       <c r="I6" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>4.506363447849684e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001063093201132382</v>
+        <v>4.371887127726141e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>4.439125287787912e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002989099998579601</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.00517720011825993</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000030960474381</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005397604245575938</v>
       </c>
       <c r="P6" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0539635462142</v>
       </c>
       <c r="Q6" t="n">
-        <v>211.081772065143</v>
+        <v>210.967637213438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999564235404542</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6578630938526802</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.999811573634766</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999406053649409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999414488810088</v>
       </c>
       <c r="G7" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.586886879139034e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2031072470338359</v>
       </c>
       <c r="I7" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>4.892358376231069e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001063093201132382</v>
+        <v>4.895983620092202e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>4.89412991440344e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002965509983007323</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005086144786711281</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029881000831</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005302672500052741</v>
       </c>
       <c r="P7" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1249405787582</v>
       </c>
       <c r="Q7" t="n">
-        <v>211.081772065143</v>
+        <v>211.038614245982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999573694759298</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6575882537018203</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997977206689975</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999345357758512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999363040370594</v>
       </c>
       <c r="G8" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.530732063077045e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2032704040198626</v>
       </c>
       <c r="I8" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>5.252040913380387e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001063093201132382</v>
+        <v>5.396308417680055e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>5.324173526066703e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002944242317521045</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005030638193188857</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029232359362</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005244802875929579</v>
       </c>
       <c r="P8" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1688337021808</v>
       </c>
       <c r="Q8" t="n">
-        <v>211.081772065143</v>
+        <v>211.0825073694047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999578388593345</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6573383597234325</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997848798263832</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999287947181041</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999314788468134</v>
       </c>
       <c r="G9" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.502867436549565e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2034187518802915</v>
       </c>
       <c r="I9" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>5.585444382920623e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001063093201132382</v>
+        <v>5.869551912884721e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>5.727498147902672e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002925039590020647</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005002866614801523</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000028910496456</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005215849003955203</v>
       </c>
       <c r="P9" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1909768314982</v>
       </c>
       <c r="Q9" t="n">
-        <v>211.081772065143</v>
+        <v>211.104650498722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999579504013776</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.657111490125773</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997730124178208</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999233907703243</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999269710807578</v>
       </c>
       <c r="G10" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.49624581903465e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2035534314737185</v>
       </c>
       <c r="I10" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>5.893573320249051e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001063093201132382</v>
+        <v>6.315006957564448e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>6.104290138906749e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002908987712433881</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.004996244408587965</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000028834010484</v>
       </c>
       <c r="O10" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005208944876713278</v>
       </c>
       <c r="P10" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1962750682445</v>
       </c>
       <c r="Q10" t="n">
-        <v>211.081772065143</v>
+        <v>211.1099487354683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999577993754926</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6569056268061024</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997620615581381</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999183461353892</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999227825595302</v>
       </c>
       <c r="G11" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.505211367969165e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2036756408331073</v>
       </c>
       <c r="I11" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.17790470895476e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001063093201132382</v>
+        <v>6.730843337177999e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>6.454397316877493e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002896336888318149</v>
       </c>
       <c r="M11" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005005208654960515</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000028937571091</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005218290749612456</v>
       </c>
       <c r="P11" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1891047111245</v>
       </c>
       <c r="Q11" t="n">
-        <v>211.081772065143</v>
+        <v>211.1027783783483</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999574602485194</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6567191304867706</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997520317260333</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999136481452754</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999189085683359</v>
       </c>
       <c r="G12" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.525343410049747e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2037863531044841</v>
       </c>
       <c r="I12" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.438322262776579e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0001063093201132382</v>
+        <v>7.118105294792616e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>6.778213778784599e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002884993109813718</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005025279504713889</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029170115301</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005239216056992217</v>
       </c>
       <c r="P12" t="n">
-        <v>139.1680983979192</v>
+        <v>139.173096815021</v>
       </c>
       <c r="Q12" t="n">
-        <v>211.081772065143</v>
+        <v>211.0867704822448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999569881190329</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.656550329719074</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997428326318448</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999092924549358</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999153318151308</v>
       </c>
       <c r="G13" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.553371055858057e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2038865605320023</v>
       </c>
       <c r="I13" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.677170289436653e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001063093201132382</v>
+        <v>7.477150998767171e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.077184919883085e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002874787285823527</v>
       </c>
       <c r="M13" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005053089209442137</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029493861235</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005268209678424772</v>
       </c>
       <c r="P13" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1510219923204</v>
       </c>
       <c r="Q13" t="n">
-        <v>211.081772065143</v>
+        <v>211.0646956595443</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999564313820629</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6563975857094264</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997344342847349</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999052770677022</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999120475119453</v>
       </c>
       <c r="G14" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.586421367377806e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2039772359743268</v>
       </c>
       <c r="I14" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.895227479994597e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001063093201132382</v>
+        <v>7.808145037270449e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.35171095363391e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002865582726815837</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005085687138802196</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029875623728</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005302195369124705</v>
       </c>
       <c r="P14" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1253005122787</v>
       </c>
       <c r="Q14" t="n">
-        <v>211.081772065143</v>
+        <v>211.0389741795026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999558224423445</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6562594004592599</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997267744027386</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999015789254174</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999090349309393</v>
       </c>
       <c r="G15" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.62257065954381e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2040592687081176</v>
       </c>
       <c r="I15" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.094110941970843e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.112988126769464e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.6035244642022e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002857267433370042</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.00512110404067698</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000030293182392</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005339120041835393</v>
       </c>
       <c r="P15" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0975409209258</v>
       </c>
       <c r="Q15" t="n">
-        <v>211.081772065143</v>
+        <v>211.0112145881496</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999551850897118</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6561345570328597</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997197885126676</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998981839940908</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999062756429841</v>
       </c>
       <c r="G16" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.660406665036201e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.204133381158984</v>
       </c>
       <c r="I16" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.275494676469911e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.392837108914815e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.834165892692363e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002849858334534094</v>
       </c>
       <c r="M16" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005157913013066623</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000030730224198</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00537749604838474</v>
       </c>
       <c r="P16" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0688929445385</v>
       </c>
       <c r="Q16" t="n">
-        <v>211.081772065143</v>
+        <v>210.9825666117624</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999545410618689</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.656021801348977</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997134465012537</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998950723727078</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999037563534308</v>
       </c>
       <c r="G17" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.698638939851923e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2042003178037287</v>
       </c>
       <c r="I17" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.440160553373559e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.649332452444941e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.04474650290925e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002843172005694271</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005194842576875571</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000029243108677</v>
+        <v>1.00003117184329</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00541599778017977</v>
       </c>
       <c r="P17" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0403558308207</v>
       </c>
       <c r="Q17" t="n">
-        <v>211.081772065143</v>
+        <v>210.9540294980446</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.999953903042166</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6559200128282796</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997076807830334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998922277153716</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999014585163156</v>
       </c>
       <c r="G18" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.73651454551244e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2042607438666498</v>
       </c>
       <c r="I18" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.58986338182457e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.883821572705157e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.236816501865465e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002837177965204509</v>
       </c>
       <c r="M18" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005231170562610667</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000031609342515</v>
       </c>
       <c r="O18" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005453872323476907</v>
       </c>
       <c r="P18" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0124808360233</v>
       </c>
       <c r="Q18" t="n">
-        <v>211.081772065143</v>
+        <v>210.9261545032471</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999532831934517</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6558280397839892</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997024497253597</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998896334979113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998993668527293</v>
       </c>
       <c r="G19" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.773311442806927e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2043153430387692</v>
       </c>
       <c r="I19" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.725684124290604e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.097666580421388e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.411653012340263e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002831681723756457</v>
       </c>
       <c r="M19" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005266223924983562</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032034381633</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005490417980056479</v>
       </c>
       <c r="P19" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9857667841101</v>
       </c>
       <c r="Q19" t="n">
-        <v>211.081772065143</v>
+        <v>210.8994404513339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999526877467191</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6557450022429001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996977025165339</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998872741055218</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998974659020201</v>
       </c>
       <c r="G20" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.808659733050748e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2043646377101948</v>
       </c>
       <c r="I20" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.848942070884348e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.292154626022152e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.57054834845325e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002826815997586843</v>
       </c>
       <c r="M20" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005299678983722267</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032442687964</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00552529728990721</v>
       </c>
       <c r="P20" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9604361174698</v>
       </c>
       <c r="Q20" t="n">
-        <v>211.081772065143</v>
+        <v>210.8741097846936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999521201544347</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6556702482212634</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996934077231661</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998851212707809</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998957370680583</v>
       </c>
       <c r="G21" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.842354462920788e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2044090149266439</v>
       </c>
       <c r="I21" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.960453367518505e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.469615833048101e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.715056910456242e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002822443661869274</v>
       </c>
       <c r="M21" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005331373615608634</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032831894102</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005558341227889912</v>
       </c>
       <c r="P21" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9365854400363</v>
       </c>
       <c r="Q21" t="n">
-        <v>211.081772065143</v>
+        <v>210.8502591072601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.999951584177343</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6556029192434304</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996895131336427</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998831642876383</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998941671214193</v>
       </c>
       <c r="G22" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.874172378386074e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2044489843163459</v>
       </c>
       <c r="I22" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.061573652107313e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.630932716314211e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.846284510243989e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002818481575305108</v>
       </c>
       <c r="M22" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005361130830698011</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000033199421251</v>
       </c>
       <c r="O22" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005589365269231572</v>
       </c>
       <c r="P22" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9143214011008</v>
       </c>
       <c r="Q22" t="n">
-        <v>211.081772065143</v>
+        <v>210.8279950683247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.999951081852235</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6555420430374795</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996859811279851</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998813908416274</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998927444707482</v>
       </c>
       <c r="G23" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.903992566723942e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2044851230619135</v>
       </c>
       <c r="I23" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.153279701005681e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.777120374714716e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.965200037860199e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002814954709530675</v>
       </c>
       <c r="M23" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005388870537249844</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000033543872753</v>
       </c>
       <c r="O23" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005618285912520424</v>
       </c>
       <c r="P23" t="n">
-        <v>139.1680983979192</v>
+        <v>138.893677855358</v>
       </c>
       <c r="Q23" t="n">
-        <v>211.081772065143</v>
+        <v>210.8073515225819</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999506158737842</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6554871136610572</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996828207103892</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998797834908218</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998914610567414</v>
       </c>
       <c r="G24" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.931655060484878e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2045177315125834</v>
       </c>
       <c r="I24" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.235337726583469e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.909616570848121e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>9.072477148715795e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.00281176365377592</v>
       </c>
       <c r="M24" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.00541447602311145</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000033863400834</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005644981476925821</v>
       </c>
       <c r="P24" t="n">
-        <v>139.1680983979192</v>
+        <v>138.8747166687178</v>
       </c>
       <c r="Q24" t="n">
-        <v>211.081772065143</v>
+        <v>210.7883903359416</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999501817841242</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6554376282626071</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996799391885024</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998783271890523</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998902954388404</v>
       </c>
       <c r="G25" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.957424497872321e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2045471081827612</v>
       </c>
       <c r="I25" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.310154420740274e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0001063093201132382</v>
+        <v>0.0001002966158168445</v>
       </c>
       <c r="K25" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>9.169908001212363e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002808792176173415</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005438220754872241</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000034161062315</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00566973707107604</v>
       </c>
       <c r="P25" t="n">
-        <v>139.1680983979192</v>
+        <v>138.8572133549259</v>
       </c>
       <c r="Q25" t="n">
-        <v>211.081772065143</v>
+        <v>210.7708870221497</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999497789158546</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6553931485939557</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996773343824424</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998770022629626</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998892375778307</v>
       </c>
       <c r="G26" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.981340498659082e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2045735132354943</v>
       </c>
       <c r="I26" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.377786382595859e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0001063093201132382</v>
+        <v>0.0001013887710976616</v>
       </c>
       <c r="K26" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>9.258331746181007e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002806305810341406</v>
       </c>
       <c r="M26" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005460165289310464</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000034437314843</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005692615829776747</v>
       </c>
       <c r="P26" t="n">
-        <v>139.1680983979192</v>
+        <v>138.8411048676642</v>
       </c>
       <c r="Q26" t="n">
-        <v>211.081772065143</v>
+        <v>210.754778534888</v>
       </c>
     </row>
   </sheetData>
